--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,6 +546,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>28136</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>27760</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>28247</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>27731.75</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>443530</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -534,6 +610,37 @@
           <t>05/01/26</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>681.61</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>677.96</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>682.77</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>677.51</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>36413121</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +674,37 @@
           <t>05/01/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>81659.74000000001</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>1643.22</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>80002.99000000001</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>81760.03</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>79749.14999999999</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,12 +730,41 @@
       <c r="G5" s="1" t="n">
         <v>97.72</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>05/01/26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v/>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>05/01/26</t>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
         </is>
       </c>
     </row>
@@ -633,6 +800,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.86365</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>-0.00033</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.86398</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.86439</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.86234</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>422054</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -666,6 +864,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.5595</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>689245</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -699,6 +928,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1.36199</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>-0.00051</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.36249</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1.36299</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1.36045</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>276788</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -732,6 +992,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.97828</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.00183</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.97644</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.97955</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.97235</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>258385</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -765,6 +1056,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -798,6 +1120,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -831,6 +1184,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>72.80800000000001</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>72.727</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>72.417</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>137144</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -864,6 +1248,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>4557.33</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>4522.54</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4586.19</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>4514.22</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>157377</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -897,6 +1312,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.5754</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.5739</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>232988</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -930,6 +1376,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1.59252</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>1.59282</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>1.59442</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1.59068</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>364907</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -963,6 +1440,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>157.892</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>157.252</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>157.919</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>157.091</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>367658</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -996,6 +1504,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.9156300000000001</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>-0.0008899999999999999</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.91653</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.91698</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.91496</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>354846</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1027,6 +1566,37 @@
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>15:59 CT</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.78307</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.7839699999999999</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.78482</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.7813099999999999</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>330923</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>05/05/26</t>
         </is>
       </c>
     </row>

--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -759,9 +759,7 @@
       <c r="R5" s="1" t="n">
         <v>98.31</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="S5" s="3" t="n"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1601,4 +1602,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>29424</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29294</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>29480</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29225.75</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>540073</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>713.29</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>710.36</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>714.59</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>708.91</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>35866961</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>81854.53</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1731.55</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>80707.83</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>82447.41</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>80489.50999999999</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>727</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>97.84999999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86573</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00123</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86605</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86725</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86298</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>384102</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5643</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>645427</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.36787</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.36949</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.36484</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>264535</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.00051</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98953</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.99215</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.98673</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>274478</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>86.102</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>5.714</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>80.318</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>86.22199999999999</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>79.17</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>188317</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4734.98</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4719.56</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4748.34</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4648.56</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>178155</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5688</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5688</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5681</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>226323</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.61164</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00027</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.61094</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.61202</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.60769</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>340223</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>157.226</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>156.551</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>157.269</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>156.551</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>276824</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.9166800000000001</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.00147</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.91621</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.91679</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.91474</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>297947</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.77799</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00152</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.77861</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.77954</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.77681</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>287436</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>05/11/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -1783,9 +1783,7 @@
       <c r="G5" s="1" t="n">
         <v>97.84999999999999</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2222,4 +2223,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>29231.75</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>-456</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29690</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>29734</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29089.75</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>739764</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>708.9299999999999</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>-10.86</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>715.13</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>705.55</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>50410055</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>05/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>79102.75999999999</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>-2356.36</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>81388.36</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>81721.21000000001</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>78670.39999999999</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>05/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>05/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.87251</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00171</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.8708</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.87292</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.8701100000000001</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>486989</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>16:00 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5659</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5663</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>831713</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.37496</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00297</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.372</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.37671</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.37152</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>340452</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.98275</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-0.00791</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.99066</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.99127</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.98222</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>339186</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>75.961</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-7.554</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>83.515</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>83.873</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>75.749</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>223147</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4540.43</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>-111.74</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4652.2</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4664.98</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4512.33</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>224298</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5722</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5713</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5728</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5706</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>243286</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.59844</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00253</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.60097</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.60196</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.59718</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>386211</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>158.771</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>158.393</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>158.845</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>158.298</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>384180</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.91474</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.9145799999999999</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.91523</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>363391</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.78687</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00309</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.78377</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.78734</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.78349</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>356713</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -2231,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2280,6 +2280,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2313,6 +2358,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>29096</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>-135.75</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>29135</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>29419.75</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>28814.75</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>839386</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2346,6 +2422,37 @@
           <t>05/15/26</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>705.88</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>711.54</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>712.0700000000001</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>698.85</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>49584367</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2379,6 +2486,37 @@
           <t>05/15/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>76939.84</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>-2162.92</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>78277.37</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>78474.5</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>76067</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>581</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2404,12 +2542,41 @@
       <c r="G5" s="1" t="n">
         <v>98.92</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>05/15/26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v/>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>05/15/26</t>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2445,6 +2612,37 @@
           <t>16:00 CT</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.86769</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>-0.00482</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.87208</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.87301</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.86656</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>490067</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2478,6 +2676,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.5623</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>858906</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2511,6 +2740,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1.37401</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>-0.00095</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.3748</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1.37635</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1.37326</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>321940</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2544,6 +2804,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.9850100000000001</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.98358</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.98661</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.97976</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>352320</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2577,6 +2868,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2610,6 +2932,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2643,6 +2996,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>77.679</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>1.718</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>75.914</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>78.172</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>73.89</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>207941</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2676,6 +3060,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>4566.21</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>4539.83</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4584</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>4481.2</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>217064</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2709,6 +3124,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>243520</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2742,6 +3188,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1.60144</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>1.59772</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>1.60196</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1.59742</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>387521</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2775,6 +3252,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>158.847</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>158.575</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>159.081</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>158.575</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>393241</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2808,6 +3316,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.91433</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>-0.00041</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.91379</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.91538</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>368036</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2839,6 +3378,37 @@
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>15:59 CT</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.78439</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>-0.00248</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.78717</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.78774</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.78403</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>359624</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
         </is>
       </c>
     </row>

--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -2571,9 +2571,7 @@
       <c r="R5" s="1" t="n">
         <v>98.95</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="S5" s="3" t="n"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3413,4 +3414,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>29558.75</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29444</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>29749</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29436</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>483608</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>717.54</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>718.0700000000001</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>722.12</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>715.95</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>32934172</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>05/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>75957.85000000001</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>-1759.79</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>77745.94</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>77891.23</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>75701.10000000001</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>05/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>99.17</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>05/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86373</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.00124</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86498</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86564</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>425879</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5594</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5594</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>704500</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.38205</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00426</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.3778</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.3825</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.37741</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>268490</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.98505</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-3e-05</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98509</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.98631</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.98246</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>274738</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-1.168</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>76.66800000000001</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>77.023</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>74.994</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>162727</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4509.5</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>-33.6</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4543.12</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4545.93</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4492.51</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>181058</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>219810</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.60359</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00298</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.60059</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.60448</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.59955</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>320255</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>159.201</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>158.985</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>159.234</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>158.915</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>340381</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.91083</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>-0.00308</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.91392</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.91474</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.91048</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>315241</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.78501</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>-0.00167</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.78668</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.78759</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.78383</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>296107</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -3422,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3471,6 +3471,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3504,6 +3549,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>29520.75</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>29444</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>29749</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>29436</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>483608</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>05/22/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3537,6 +3613,37 @@
           <t>05/22/26</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>717.54</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>718.0700000000001</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>722.12</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>715.95</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>33118500</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>05/22/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3570,6 +3677,37 @@
           <t>05/22/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>77286.37</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>1328.52</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>76641.86</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>77875.41</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>76103.72</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1452</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3595,12 +3733,41 @@
       <c r="G5" s="1" t="n">
         <v>99.17</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>05/22/26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v/>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>05/22/26</t>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3636,6 +3803,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.86209</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>-0.00164</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.86461</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.86512</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.86181</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>207960</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3669,6 +3867,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.5622</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.5595</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>347917</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3702,6 +3931,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1.38028</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>-0.00177</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.3805</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1.38205</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1.37949</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>173961</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3735,6 +3995,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.99038</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.98909</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.9908</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.98749</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>184851</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3768,6 +4059,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3801,6 +4123,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3834,6 +4187,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>78.072</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>75.601</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>78.81999999999999</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>75.601</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>139924</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3867,6 +4251,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>4570.38</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>4511.98</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4579.15</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>4511.98</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>121472</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3900,6 +4315,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.5655</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>63200</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3933,6 +4379,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1.6071</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>1.60489</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>1.60868</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1.60489</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>255673</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3966,6 +4443,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>158.916</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>158.757</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>159.039</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>158.757</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>223783</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3999,6 +4507,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.91132</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0.00049</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.91346</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.91346</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.90968</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>195771</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4030,6 +4569,37 @@
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>15:59 CT</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.7827</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>-0.00231</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.78447</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.78447</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.78082</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>151794</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>05/25/26</t>
         </is>
       </c>
     </row>

--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Week5" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3762,9 +3763,7 @@
       <c r="R5" s="1" t="n">
         <v>98.92</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="S5" s="3" t="n"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
@@ -4600,6 +4599,628 @@
       <c r="T18" s="4" t="inlineStr">
         <is>
           <t>05/25/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>30405.25</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>30328</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>30536</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>30216.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>566984</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>738.3099999999999</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>737.84</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>741.63</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>735.25</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>36950813</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>05/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>73670.96000000001</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>73601.09</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>74368.12</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>72533.89999999999</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>05/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>98.94</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>16:59 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-4e-05</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86653</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86816</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86552</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>417924</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5611</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5602</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>684816</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.37976</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00138</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.37837</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.38293</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.37708</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>310758</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.99122</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.00392</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98731</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.99319</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.98638</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>279192</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>75.285</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-0.377</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>75.66200000000001</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>76.64400000000001</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>74.629</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>155719</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4540.33</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4495.87</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4594.43</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4489.5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>167886</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5688</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>235920</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.60867</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00297</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.6057</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.6107</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.60442</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>387325</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>159.279</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>159.243</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>159.379</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>159.101</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>285985</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.9105799999999999</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>-0.00274</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.91332</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.91359</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.90976</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>344301</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.78098</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>-0.00299</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.7839699999999999</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.78472</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.77957</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>313375</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
         </is>
       </c>
     </row>

--- a/outputs/may.xlsx
+++ b/outputs/may.xlsx
@@ -4786,9 +4786,7 @@
       <c r="G5" s="1" t="n">
         <v>98.75</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>16:59 ET</t>
